--- a/data/trans_dic/IP11A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP11A_R-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,18</t>
+          <t>0,0; 70,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,99</t>
+          <t>0,0; 76,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,45</t>
+          <t>0,0; 55,5</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 57,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,18</t>
+          <t>0,0; 42,39</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 57,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,23</t>
+          <t>0,0; 45,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
           <t>17,28%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 24,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,82</t>
+          <t>0,0; 25,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,51</t>
+          <t>0,0; 43,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 55,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,72</t>
+          <t>0,0; 14,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,48</t>
+          <t>0,0; 9,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 27,02</t>
+          <t>2,87; 25,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,46</t>
+          <t>0,0; 26,46</t>
         </is>
       </c>
     </row>
@@ -1209,37 +1209,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>20,66%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 34,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 21,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,17 +1297,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 58,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,45</t>
+          <t>0,0; 26,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,2</t>
+          <t>0,0; 12,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,57</t>
+          <t>0,0; 27,28</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>12,43%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 10,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,91; 26,58</t>
+          <t>0,0; 9,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,91</t>
+          <t>0,0; 24,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 11,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,92</t>
+          <t>3,17; 26,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,22</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,25</t>
+          <t>0,61; 6,14</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,67</t>
+          <t>0,0; 3,57</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 13,01</t>
+          <t>2,22; 13,17</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 17,59</t>
+          <t>2,51; 16,81</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>568</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>689</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1257</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2816</t>
+          <t>0; 2369</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3055</t>
+          <t>0; 2664</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3964</t>
+          <t>0; 3794</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>988</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>988</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3879</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4432</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 4111</t>
+          <t>0; 3936</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>713</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3284</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2922</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2951</t>
+          <t>0; 2916</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,54 +2483,54 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>695</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>628</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>1389</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>628</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
           <t>1977</t>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>592</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3512</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2668</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3763</t>
+          <t>0; 3137</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3048</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2848</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3568</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3022</t>
+          <t>0; 3464</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2876</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3467</t>
+          <t>0; 4050</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 2599</t>
+          <t>0; 3626</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>576; 5505</t>
+          <t>584; 5265</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3425</t>
+          <t>0; 3067</t>
         </is>
       </c>
     </row>
@@ -2623,37 +2623,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2691,37 +2691,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>641</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
           <t>1362</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1131</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3828</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2857</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3665</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2779,17 +2779,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3684</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2939</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3869</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2799,17 +2799,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4277</t>
+          <t>0; 3714</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 3268</t>
+          <t>0; 3331</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4561</t>
+          <t>0; 4207</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3039,37 +3039,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3107,54 +3107,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
           <t>2751</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1344</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>1826</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>1269</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
           <t>4052</t>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>2838</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4644</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3931</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>645; 5880</t>
+          <t>0; 4004</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4444</t>
+          <t>0; 5363</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>485; 4991</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 4451</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 4041</t>
+          <t>701; 5791</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 5821</t>
+          <t>0; 4055</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>482; 4952</t>
+          <t>485; 4864</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 4449</t>
+          <t>0; 4322</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1408; 8175</t>
+          <t>1396; 8277</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1024; 7244</t>
+          <t>990; 6628</t>
         </is>
       </c>
     </row>
